--- a/Supplementary_Materials/SAST_detection.xlsx
+++ b/Supplementary_Materials/SAST_detection.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Supplementary_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681A4705-50FF-4D51-930D-DA5A24116886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8DE67C-17B1-4979-A9DA-14144F26F666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>Tool in InterPVD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,18 +38,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,6 +101,82 @@
   </si>
   <si>
     <t>P-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP/TPR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/1.41%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FP/FPR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/0.80%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>196/39.44%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>181/36.42%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38/7.65%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30/6.04%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>215/43.26%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>187/37.63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>354/71.23%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>253/50.91%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/2.21%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>43/8.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/0.20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59/11.87%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14/2.82%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>226/45.47%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54/10.87%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -202,9 +270,6 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -213,6 +278,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -260,9 +328,9 @@
   <autoFilter ref="A2:I7" xr:uid="{4410437C-AC61-48A6-A9EA-F041E878FDAB}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{BC2B19AB-ABCA-4914-AD93-8D8FA67B6775}" name="Tool in InterPVD (for source code, no compilation)"/>
-    <tableColumn id="2" xr3:uid="{0409A9EC-8ACE-4878-9C49-87B67E78D6ED}" name="TP"/>
+    <tableColumn id="2" xr3:uid="{0409A9EC-8ACE-4878-9C49-87B67E78D6ED}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{E3EE4851-F24D-4FCD-BC1C-84BF16372D01}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{5C019BB4-0CAA-4E20-B39D-817C16D05BB8}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{5C019BB4-0CAA-4E20-B39D-817C16D05BB8}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{47B6186F-DC3D-43B8-8268-E9D59DFF1E4C}" name="FN"/>
     <tableColumn id="6" xr3:uid="{3063C665-4442-4017-B579-C45FCC7CE758}" name="Precision" dataDxfId="7"/>
     <tableColumn id="7" xr3:uid="{CD7AA765-0969-4AE2-BE9F-1C4CF36CF4DA}" name="Recall" dataDxfId="6"/>
@@ -278,9 +346,9 @@
   <autoFilter ref="A11:I16" xr:uid="{B7987D76-D05D-4F5F-9869-9556AFCAC343}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5B1AAAEC-15FF-43EF-9F6E-C7958971ADAB}" name="Tool in InterPVD"/>
-    <tableColumn id="2" xr3:uid="{F36B85B7-A6DE-483A-8E24-EEF76B70A5C8}" name="TP"/>
+    <tableColumn id="2" xr3:uid="{F36B85B7-A6DE-483A-8E24-EEF76B70A5C8}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{0FD9E1BB-E379-4831-AAC0-B2CE922FD5E4}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{0D6DA9F7-E545-4DFE-A228-FFE450C8E872}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{0D6DA9F7-E545-4DFE-A228-FFE450C8E872}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{9885DB22-CC9F-4EA5-A7FC-B9F9EFC71373}" name="FN"/>
     <tableColumn id="6" xr3:uid="{CA3A5A0E-5A6B-4BB2-BBE0-F4F3F7199815}" name="Precision" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{53F07C16-5F33-4F5E-BE34-1873DD1FAA8A}" name="Recall" dataDxfId="2"/>
@@ -577,64 +645,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="A1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3">
         <v>493</v>
       </c>
-      <c r="D3" s="4">
-        <v>4</v>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="E3">
         <v>490</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>0.63639999999999997</v>
       </c>
       <c r="G3" s="1">
@@ -649,16 +717,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>196</v>
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>316</v>
       </c>
-      <c r="D4">
-        <v>181</v>
+      <c r="D4" t="s">
+        <v>24</v>
       </c>
       <c r="E4">
         <v>301</v>
@@ -678,16 +746,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
       </c>
       <c r="C5">
         <v>467</v>
       </c>
-      <c r="D5">
-        <v>30</v>
+      <c r="D5" t="s">
+        <v>26</v>
       </c>
       <c r="E5">
         <v>459</v>
@@ -707,16 +775,16 @@
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>215</v>
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
       </c>
       <c r="C6">
         <v>310</v>
       </c>
-      <c r="D6">
-        <v>187</v>
+      <c r="D6" t="s">
+        <v>28</v>
       </c>
       <c r="E6">
         <v>282</v>
@@ -735,88 +803,88 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4">
-        <v>354</v>
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C7">
         <v>244</v>
       </c>
-      <c r="D7">
-        <v>253</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3">
         <v>143</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>0.58320000000000005</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>0.71230000000000004</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0.6431</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>0.60160000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="A10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>5</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>6</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>1</v>
       </c>
-      <c r="B12">
-        <v>4</v>
+      <c r="B12" t="s">
+        <v>22</v>
       </c>
       <c r="C12">
         <v>486</v>
       </c>
-      <c r="D12">
-        <v>11</v>
+      <c r="D12" t="s">
+        <v>31</v>
       </c>
       <c r="E12">
         <v>493</v>
@@ -836,16 +904,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
       </c>
       <c r="C13">
         <v>486</v>
       </c>
-      <c r="D13">
-        <v>11</v>
+      <c r="D13" t="s">
+        <v>31</v>
       </c>
       <c r="E13">
         <v>454</v>
@@ -865,16 +933,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3">
         <v>496</v>
       </c>
-      <c r="D14" s="4">
-        <v>1</v>
+      <c r="D14" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E14">
         <v>486</v>
@@ -894,21 +962,21 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>59</v>
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
       </c>
       <c r="C15">
         <v>483</v>
       </c>
-      <c r="D15">
-        <v>14</v>
+      <c r="D15" t="s">
+        <v>35</v>
       </c>
       <c r="E15">
         <v>438</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>0.80820000000000003</v>
       </c>
       <c r="G15" s="1">
@@ -922,58 +990,58 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>226</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5">
         <v>443</v>
       </c>
-      <c r="D16" s="6">
-        <v>54</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="3">
         <v>271</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>0.80810000000000004</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>0.45739999999999997</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>0.58169999999999999</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>0.67300000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="A19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -983,7 +1051,7 @@
       <c r="B21" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>0</v>
       </c>
       <c r="D21" s="1">
@@ -995,7 +1063,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1">
         <v>8.0500000000000002E-2</v>
@@ -1012,24 +1080,24 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>0</v>
       </c>
       <c r="D23" s="1">
         <v>0.97589999999999999</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>2E-3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1">
         <v>0.1066</v>
@@ -1045,16 +1113,16 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="5">
+      <c r="A25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="4">
         <v>0.36199999999999999</v>
       </c>
       <c r="C25" s="1">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>0.52900000000000003</v>
       </c>
       <c r="E25" s="1">
